--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_6_R1.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_6_R1.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. HOLMES</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6042</v>
+        <v>3.2587</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8117</v>
+        <v>2.2848</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7925</v>
+        <v>0.9739</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0726</v>
+        <v>3.2774</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0096</v>
+        <v>0.8415</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9370000000000001</v>
+        <v>2.4359</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5318000000000001</v>
+        <v>2.4772</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0939</v>
+        <v>0.9817</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6257</v>
+        <v>1.4956</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6044</v>
+        <v>0.8002</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9157</v>
+        <v>-0.1401</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3113</v>
+        <v>0.9403</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06850000000000001</v>
+        <v>-1.0341</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7591</v>
+        <v>0.0395</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6906</v>
+        <v>-1.0736</v>
       </c>
       <c r="V2" t="n">
-        <v>2.6805</v>
+        <v>-1.0722</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. ROGKAVOPOULOS</t>
+          <t>R. HOLMES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8672</v>
+        <v>3.0384</v>
       </c>
       <c r="E3" t="n">
-        <v>2.932</v>
+        <v>2.1786</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.8598</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4412</v>
+        <v>-0.0726</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-1.0096</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2705</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5244</v>
+        <v>-0.0939</v>
       </c>
       <c r="L3" t="n">
-        <v>0.746</v>
+        <v>0.6257</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8293</v>
+        <v>-0.6044</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.612</v>
+        <v>-0.9157</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2173</v>
+        <v>0.3113</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0523</v>
+        <v>-0.4973</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5351</v>
+        <v>0.1261</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4828</v>
+        <v>-0.6234</v>
       </c>
       <c r="V3" t="n">
-        <v>1.214</v>
+        <v>2.6805</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2862</v>
+        <v>2.6805</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>N. ROGKAVOPOULOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7122</v>
+        <v>2.2006</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7383</v>
+        <v>2.2989</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9739</v>
+        <v>-0.0983</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2774</v>
+        <v>0.4412</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8415</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4359</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4772</v>
+        <v>1.2705</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9817</v>
+        <v>0.5244</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4956</v>
+        <v>0.746</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8002</v>
+        <v>-0.8293</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1401</v>
+        <v>-0.612</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9403</v>
+        <v>-0.2173</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5806</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.507</v>
+        <v>-0.098</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0736</v>
+        <v>-0.5164</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X4" t="n">
         <v>-1.0722</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. YURTSEVEN</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0726</v>
+        <v>2.096</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4468</v>
+        <v>3.0084</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3742</v>
+        <v>-0.9123</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4813</v>
+        <v>2.7589</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9291</v>
+        <v>5.0475</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5522</v>
+        <v>-2.2886</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3633</v>
+        <v>4.1674</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7008</v>
+        <v>6.3424</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6625</v>
+        <v>-2.175</v>
       </c>
       <c r="M5" t="n">
-        <v>0.118</v>
+        <v>-1.4085</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2283</v>
+        <v>-1.2949</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1103</v>
+        <v>-0.1136</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.7834</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.7112</v>
+        <v>-2.3195</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3721</v>
+        <v>-1.5933</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5780999999999999</v>
+        <v>-0.4479</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.206</v>
+        <v>-1.1455</v>
       </c>
       <c r="V5" t="n">
-        <v>2.0026</v>
+        <v>0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>3.2166</v>
+        <v>1.6083</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.214</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4495</v>
+        <v>1.6833</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2222</v>
+        <v>1.4895</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2274</v>
+        <v>0.1938</v>
       </c>
       <c r="G6" t="n">
         <v>1.1811</v>
@@ -922,13 +922,13 @@
         <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0365</v>
+        <v>0.2702</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2161</v>
+        <v>0.0512</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2526</v>
+        <v>0.219</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>O. YURTSEVEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3905</v>
+        <v>1.5656</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2692</v>
+        <v>2.2423</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8787</v>
+        <v>-0.6767</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7589</v>
+        <v>2.4813</v>
       </c>
       <c r="H7" t="n">
-        <v>5.0475</v>
+        <v>1.9291</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.2886</v>
+        <v>0.5522</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1674</v>
+        <v>2.3633</v>
       </c>
       <c r="K7" t="n">
-        <v>6.3424</v>
+        <v>1.7008</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.175</v>
+        <v>0.6625</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4085</v>
+        <v>0.118</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2949</v>
+        <v>0.2283</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1136</v>
+        <v>-0.1103</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>-3.7112</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.2989</v>
+        <v>-0.1349</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.187</v>
+        <v>0.3736</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1119</v>
+        <v>-0.5085</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9304</v>
+        <v>2.0026</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6083</v>
+        <v>3.2166</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4669</v>
+        <v>0.785</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6415</v>
+        <v>2.0268</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1746</v>
+        <v>-1.2418</v>
       </c>
       <c r="G8" t="n">
         <v>1.3681</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1511</v>
+        <v>0.1669</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0158</v>
+        <v>0.4011</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1669</v>
+        <v>-0.2341</v>
       </c>
       <c r="V8" t="n">
         <v>-1.214</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>M. GRIGONIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1705</v>
+        <v>-0.1573</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-1.135</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5508</v>
+        <v>0.9777</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3008</v>
+        <v>-0.2749</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5619</v>
+        <v>0.826</v>
       </c>
       <c r="I9" t="n">
-        <v>0.261</v>
+        <v>-1.1009</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6652</v>
+        <v>-1.1862</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6652</v>
+        <v>0.3865</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.5727</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3644</v>
+        <v>0.9113</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1034</v>
+        <v>0.4395</v>
       </c>
       <c r="O9" t="n">
-        <v>0.261</v>
+        <v>0.4718</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0294</v>
+        <v>-0.2045</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5702</v>
+        <v>0.2831</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5996</v>
+        <v>-0.4876</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-0.1418</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. GRIGONIS</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4843</v>
+        <v>-0.3996</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3276</v>
+        <v>-1.1184</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8433</v>
+        <v>0.7188</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2749</v>
+        <v>-0.3008</v>
       </c>
       <c r="H10" t="n">
-        <v>0.826</v>
+        <v>-0.5619</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1009</v>
+        <v>0.261</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1862</v>
+        <v>-0.6652</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3865</v>
+        <v>-0.6652</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5727</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9113</v>
+        <v>0.3644</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4395</v>
+        <v>0.1034</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4718</v>
+        <v>0.261</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.232</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5316</v>
+        <v>-0.2585</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0905</v>
+        <v>0.1731</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.622</v>
+        <v>-0.4316</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X10" t="n">
         <v>-0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5186</v>
+        <v>-2.9989</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2315</v>
+        <v>-2.8462</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2871</v>
+        <v>-0.1527</v>
       </c>
       <c r="G11" t="n">
         <v>-2.075</v>
@@ -1312,13 +1312,13 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9796</v>
+        <v>-0.4599</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4402</v>
+        <v>-0.0549</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5395</v>
+        <v>-0.405</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9392</v>
+        <v>-3.501</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9871</v>
+        <v>-3.5153</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0478</v>
+        <v>0.0142</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9732</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6619</v>
+        <v>-1.2237</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5895</v>
+        <v>-0.1177</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0723</v>
+        <v>-1.1059</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,31 +1423,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.450500000000002</v>
+        <v>7.5708</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7942</v>
+        <v>6.914400000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6564</v>
+        <v>0.6563999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>5.811500000000001</v>
+        <v>5.811499999999997</v>
       </c>
       <c r="H13" t="n">
-        <v>5.827800000000002</v>
+        <v>5.8278</v>
       </c>
       <c r="I13" t="n">
         <v>-0.01649999999999996</v>
       </c>
       <c r="J13" t="n">
-        <v>8.243600000000001</v>
+        <v>8.243599999999997</v>
       </c>
       <c r="K13" t="n">
-        <v>9.264799999999997</v>
+        <v>9.264800000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.021199999999999</v>
+        <v>-1.0212</v>
       </c>
       <c r="M13" t="n">
         <v>-2.4322</v>
@@ -1468,10 +1468,10 @@
         <v>15.077</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.7037</v>
+        <v>-5.5835</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.391</v>
+        <v>0.7292</v>
       </c>
       <c r="U13" t="n">
         <v>-6.312600000000001</v>
@@ -1483,7 +1483,7 @@
         <v>9.539099999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.675699999999999</v>
+        <v>-5.6757</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0149</v>
+        <v>3.6109</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6797</v>
+        <v>4.0283</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6647</v>
+        <v>-0.4174</v>
       </c>
       <c r="G14" t="n">
         <v>1.2343</v>
@@ -1546,13 +1546,13 @@
         <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3889</v>
+        <v>0.9849</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8546</v>
+        <v>1.2032</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4657</v>
+        <v>-0.2183</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6723</v>
+        <v>3.6108</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5333</v>
+        <v>3.4153</v>
       </c>
       <c r="F15" t="n">
-        <v>0.139</v>
+        <v>0.1954</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9389999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7374</v>
+        <v>1.6759</v>
       </c>
       <c r="T15" t="n">
-        <v>0.767</v>
+        <v>0.6491</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9704</v>
+        <v>1.0269</v>
       </c>
       <c r="V15" t="n">
         <v>3.1058</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0294</v>
+        <v>3.4778</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0418</v>
+        <v>3.7495</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0124</v>
+        <v>-0.2717</v>
       </c>
       <c r="G16" t="n">
         <v>3.1543</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9805</v>
+        <v>0.4679</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8136</v>
+        <v>-0.1059</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1669</v>
+        <v>0.5737</v>
       </c>
       <c r="V16" t="n">
         <v>-1.0722</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1524</v>
+        <v>-0.3998</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7285</v>
+        <v>0.2567</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8809</v>
+        <v>-0.6564</v>
       </c>
       <c r="G17" t="n">
         <v>0.3206</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5992</v>
+        <v>0.3519</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7117</v>
+        <v>0.2399</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1125</v>
+        <v>0.112</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.988</v>
+        <v>-1.3139</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0301</v>
+        <v>-0.6776</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0181</v>
+        <v>-0.6364</v>
       </c>
       <c r="G18" t="n">
         <v>0.07489999999999999</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3831</v>
+        <v>0.0571</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1325</v>
+        <v>0.4248</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7494</v>
+        <v>-0.3677</v>
       </c>
       <c r="V18" t="n">
         <v>-1.214</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.139</v>
+        <v>-1.3228</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.7038</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4248</v>
+        <v>-0.6191</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9209000000000001</v>
+        <v>-0.6399</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5495</v>
+        <v>-0.6399</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3714</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2092</v>
+        <v>-0.7863</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4201</v>
+        <v>-0.7863</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2109</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1302</v>
+        <v>0.1465</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9696</v>
+        <v>0.1465</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1605</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>2.6195</v>
+        <v>-0.0747</v>
       </c>
       <c r="T19" t="n">
-        <v>1.3961</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2235</v>
+        <v>-0.1573</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3228</v>
+        <v>-1.5048</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7038</v>
+        <v>0.0068</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6191</v>
+        <v>-1.5116</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6399</v>
+        <v>-1.0601</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6399</v>
+        <v>0.904</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-1.9641</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7863</v>
+        <v>0.9099</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7863</v>
+        <v>2.1881</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.2783</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1465</v>
+        <v>-1.97</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1465</v>
+        <v>-1.2842</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.6859</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0747</v>
+        <v>1.666</v>
       </c>
       <c r="T20" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.9911</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1573</v>
+        <v>0.675</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>-1.1829</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.4254</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6057</v>
+        <v>-1.6683</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0068</v>
+        <v>-1.8992</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6124</v>
+        <v>0.2308</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0601</v>
+        <v>-3.7984</v>
       </c>
       <c r="H21" t="n">
-        <v>0.904</v>
+        <v>-2.2893</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9641</v>
+        <v>-1.5091</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9099</v>
+        <v>-2.7043</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1881</v>
+        <v>-0.9341</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2783</v>
+        <v>-1.7702</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.97</v>
+        <v>-1.0942</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2842</v>
+        <v>-1.3552</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6859</v>
+        <v>0.261</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5652</v>
+        <v>0.8955</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9911</v>
+        <v>0.8927</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5742</v>
+        <v>0.0029</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1829</v>
+        <v>1.4665</v>
       </c>
       <c r="W21" t="n">
-        <v>0.4254</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.6083</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1065</v>
+        <v>-2.0591</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.371</v>
+        <v>-1.4219</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2644</v>
+        <v>-0.6372</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7984</v>
+        <v>-0.9209000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2893</v>
+        <v>-0.5495</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5091</v>
+        <v>-0.3714</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.7043</v>
+        <v>0.2092</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9341</v>
+        <v>0.4201</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.7702</v>
+        <v>-0.2109</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0942</v>
+        <v>-1.1302</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3552</v>
+        <v>-0.9696</v>
       </c>
       <c r="O22" t="n">
-        <v>0.261</v>
+        <v>-0.1605</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4573</v>
+        <v>1.6994</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4208</v>
+        <v>0.6884</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0365</v>
+        <v>1.0111</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4665</v>
+        <v>-1.214</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3943</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. BALDWIN</t>
+          <t>S. JOVIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8856</v>
+        <v>-2.1033</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7482</v>
+        <v>-1.4295</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1373</v>
+        <v>-0.6738</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4034</v>
+        <v>-0.0051</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.7718</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3684</v>
+        <v>-0.0736</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1687</v>
+        <v>1.0392</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.203</v>
+        <v>1.163</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3717</v>
+        <v>-0.1239</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-1.0443</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5688</v>
+        <v>-1.0945</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0033</v>
+        <v>0.0502</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9278</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0183</v>
+        <v>1.5255</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5975</v>
+        <v>1.0106</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4208</v>
+        <v>0.5149</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3533</v>
+        <v>-2.1624</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6483</v>
+        <v>-3.7047</v>
       </c>
       <c r="F24" t="n">
-        <v>1.295</v>
+        <v>1.5423</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8288</v>
@@ -2326,13 +2326,13 @@
         <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9883999999999999</v>
+        <v>0.2025</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5816</v>
+        <v>0.362</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4068</v>
+        <v>-0.1595</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S. JOVIC</t>
+          <t>K. BALDWIN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.6138</v>
+        <v>-2.2565</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.491</v>
+        <v>-2.2764</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1228</v>
+        <v>0.0199</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0051</v>
+        <v>-0.4034</v>
       </c>
       <c r="H25" t="n">
-        <v>0.06850000000000001</v>
+        <v>-1.7718</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0736</v>
+        <v>1.3684</v>
       </c>
       <c r="J25" t="n">
-        <v>1.0392</v>
+        <v>0.1687</v>
       </c>
       <c r="K25" t="n">
-        <v>1.163</v>
+        <v>-1.203</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.1239</v>
+        <v>1.3717</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0443</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0945</v>
+        <v>-0.5688</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0502</v>
+        <v>-0.0033</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.5515</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0149</v>
+        <v>-0.3892</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.051</v>
+        <v>-0.1256</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0659</v>
+        <v>-0.2636</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="26">
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.4505</v>
+        <v>-4.0914</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6563000000000012</v>
+        <v>-0.6564999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.7941</v>
+        <v>-3.4352</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.8115</v>
+        <v>-5.811500000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.827799999999999</v>
+        <v>-5.8278</v>
       </c>
       <c r="I26" t="n">
-        <v>0.01630000000000054</v>
+        <v>0.01630000000000087</v>
       </c>
       <c r="J26" t="n">
         <v>2.4322</v>
@@ -2461,7 +2461,7 @@
         <v>3.436999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.005000000000001</v>
+        <v>-1.005</v>
       </c>
       <c r="M26" t="n">
         <v>-8.2438</v>
@@ -2482,22 +2482,22 @@
         <v>11.5976</v>
       </c>
       <c r="S26" t="n">
-        <v>6.703600000000001</v>
+        <v>9.0627</v>
       </c>
       <c r="T26" t="n">
-        <v>6.3127</v>
+        <v>6.312899999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3911000000000002</v>
+        <v>2.7501</v>
       </c>
       <c r="V26" t="n">
         <v>-3.8635</v>
       </c>
       <c r="W26" t="n">
-        <v>5.675599999999999</v>
+        <v>5.6756</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.539100000000001</v>
+        <v>-9.539099999999999</v>
       </c>
     </row>
   </sheetData>
